--- a/data/team_stats/2025-26NBA_RegularSeason_Team_stats.xlsx
+++ b/data/team_stats/2025-26NBA_RegularSeason_Team_stats.xlsx
@@ -1621,19 +1621,19 @@
         <v>681</v>
       </c>
       <c r="J2" t="n">
-        <v>8197</v>
+        <v>8221</v>
       </c>
       <c r="K2" t="n">
-        <v>8249</v>
+        <v>8225</v>
       </c>
       <c r="L2" t="n">
-        <v>2184</v>
+        <v>2205</v>
       </c>
       <c r="M2" t="n">
-        <v>1934</v>
+        <v>1915</v>
       </c>
       <c r="N2" t="n">
-        <v>1001</v>
+        <v>1004</v>
       </c>
       <c r="O2" t="n">
         <v>16446</v>
@@ -1981,7 +1981,7 @@
         <v>2575</v>
       </c>
       <c r="DZ2" t="n">
-        <v>2165</v>
+        <v>2186</v>
       </c>
       <c r="EA2" t="n">
         <v>116</v>
@@ -2128,16 +2128,16 @@
         <v>0.5950782997762863</v>
       </c>
       <c r="FW2" t="n">
-        <v>14.03415883859949</v>
+        <v>13.99318817662085</v>
       </c>
       <c r="FX2" t="n">
-        <v>14.75597042065705</v>
+        <v>14.7990273556231</v>
       </c>
       <c r="FY2" t="n">
-        <v>13.44510186653654</v>
+        <v>13.40585086972388</v>
       </c>
       <c r="FZ2" t="n">
-        <v>14.15821311674142</v>
+        <v>14.19952583586626</v>
       </c>
       <c r="GA2" t="n">
         <v>0.3091767881241566</v>
@@ -2281,7 +2281,7 @@
         <v>25.18057253136056</v>
       </c>
       <c r="HV2" t="n">
-        <v>0.2664389410760034</v>
+        <v>0.2682155455540688</v>
       </c>
     </row>
     <row r="3">
@@ -2325,19 +2325,19 @@
         <v>144</v>
       </c>
       <c r="J3" t="n">
-        <v>8061</v>
+        <v>8096</v>
       </c>
       <c r="K3" t="n">
-        <v>8125</v>
+        <v>8090</v>
       </c>
       <c r="L3" t="n">
-        <v>2189</v>
+        <v>2216</v>
       </c>
       <c r="M3" t="n">
-        <v>1831</v>
+        <v>1801</v>
       </c>
       <c r="N3" t="n">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="O3" t="n">
         <v>16186</v>
@@ -2683,7 +2683,7 @@
         <v>2617</v>
       </c>
       <c r="DZ3" t="n">
-        <v>2171</v>
+        <v>2198</v>
       </c>
       <c r="EA3" t="n">
         <v>110</v>
@@ -2830,16 +2830,16 @@
         <v>0.5754985754985755</v>
       </c>
       <c r="FW3" t="n">
-        <v>14.91446470661208</v>
+        <v>14.84998764822134</v>
       </c>
       <c r="FX3" t="n">
-        <v>14.30578461538462</v>
+        <v>14.3676761433869</v>
       </c>
       <c r="FY3" t="n">
-        <v>14.40373402803622</v>
+        <v>14.34146492094862</v>
       </c>
       <c r="FZ3" t="n">
-        <v>13.71166769230769</v>
+        <v>13.77098887515451</v>
       </c>
       <c r="GA3" t="n">
         <v>0.2635614060465789</v>
@@ -2983,7 +2983,7 @@
         <v>25.89648278415401</v>
       </c>
       <c r="HV3" t="n">
-        <v>0.2715543977174048</v>
+        <v>0.2737154150197628</v>
       </c>
     </row>
     <row r="4">
@@ -3018,7 +3018,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>237660</v>
+        <v>237663</v>
       </c>
       <c r="H4" t="n">
         <v>82</v>
@@ -3027,19 +3027,19 @@
         <v>-46</v>
       </c>
       <c r="J4" t="n">
-        <v>8157</v>
+        <v>8194</v>
       </c>
       <c r="K4" t="n">
-        <v>8223</v>
+        <v>8186</v>
       </c>
       <c r="L4" t="n">
-        <v>1871</v>
+        <v>1900</v>
       </c>
       <c r="M4" t="n">
-        <v>2108</v>
+        <v>2076</v>
       </c>
       <c r="N4" t="n">
-        <v>1014</v>
+        <v>1019</v>
       </c>
       <c r="O4" t="n">
         <v>16380</v>
@@ -3387,7 +3387,7 @@
         <v>2204</v>
       </c>
       <c r="DZ4" t="n">
-        <v>1856</v>
+        <v>1885</v>
       </c>
       <c r="EA4" t="n">
         <v>144</v>
@@ -3528,22 +3528,22 @@
         <v>0.04226140498180801</v>
       </c>
       <c r="FU4" t="n">
-        <v>99.24766473112851</v>
+        <v>99.24641193622902</v>
       </c>
       <c r="FV4" t="n">
         <v>0.6127167630057804</v>
       </c>
       <c r="FW4" t="n">
-        <v>15.03112663969597</v>
+        <v>14.96361972174762</v>
       </c>
       <c r="FX4" t="n">
-        <v>13.99137784263651</v>
+        <v>14.05461763987295</v>
       </c>
       <c r="FY4" t="n">
-        <v>14.39087899963222</v>
+        <v>14.32626311935562</v>
       </c>
       <c r="FZ4" t="n">
-        <v>13.36659370059589</v>
+        <v>13.42700952846323</v>
       </c>
       <c r="GA4" t="n">
         <v>0.2532458657919913</v>
@@ -3687,7 +3687,7 @@
         <v>25.68349004424779</v>
       </c>
       <c r="HV4" t="n">
-        <v>0.2293735441951698</v>
+        <v>0.2318769831584086</v>
       </c>
     </row>
     <row r="5">
@@ -3731,19 +3731,19 @@
         <v>191</v>
       </c>
       <c r="J5" t="n">
-        <v>8464</v>
+        <v>8484</v>
       </c>
       <c r="K5" t="n">
-        <v>8526</v>
+        <v>8506</v>
       </c>
       <c r="L5" t="n">
-        <v>2247</v>
+        <v>2262</v>
       </c>
       <c r="M5" t="n">
-        <v>2230</v>
+        <v>2219</v>
       </c>
       <c r="N5" t="n">
-        <v>1027</v>
+        <v>1030</v>
       </c>
       <c r="O5" t="n">
         <v>16990</v>
@@ -4089,7 +4089,7 @@
         <v>2610</v>
       </c>
       <c r="DZ5" t="n">
-        <v>2238</v>
+        <v>2253</v>
       </c>
       <c r="EA5" t="n">
         <v>127</v>
@@ -4236,16 +4236,16 @@
         <v>0.5472779369627507</v>
       </c>
       <c r="FW5" t="n">
-        <v>13.17061672967864</v>
+        <v>13.13956859971712</v>
       </c>
       <c r="FX5" t="n">
-        <v>14.659148486981</v>
+        <v>14.69361627086762</v>
       </c>
       <c r="FY5" t="n">
-        <v>12.59836956521739</v>
+        <v>12.56867043847242</v>
       </c>
       <c r="FZ5" t="n">
-        <v>14.05626319493314</v>
+        <v>14.08931342581707</v>
       </c>
       <c r="GA5" t="n">
         <v>0.2849532224532225</v>
@@ -4389,7 +4389,7 @@
         <v>25.37698744769875</v>
       </c>
       <c r="HV5" t="n">
-        <v>0.2654773156899811</v>
+        <v>0.2666195190947666</v>
       </c>
     </row>
     <row r="6">
@@ -4433,19 +4433,19 @@
         <v>-493</v>
       </c>
       <c r="J6" t="n">
-        <v>8274</v>
+        <v>8304</v>
       </c>
       <c r="K6" t="n">
-        <v>8334</v>
+        <v>8304</v>
       </c>
       <c r="L6" t="n">
-        <v>1993</v>
+        <v>2017</v>
       </c>
       <c r="M6" t="n">
-        <v>2261</v>
+        <v>2235</v>
       </c>
       <c r="N6" t="n">
-        <v>1011</v>
+        <v>1016</v>
       </c>
       <c r="O6" t="n">
         <v>16608</v>
@@ -4793,7 +4793,7 @@
         <v>2218</v>
       </c>
       <c r="DZ6" t="n">
-        <v>1977</v>
+        <v>2001</v>
       </c>
       <c r="EA6" t="n">
         <v>155</v>
@@ -4940,16 +4940,16 @@
         <v>0.5852417302798982</v>
       </c>
       <c r="FW6" t="n">
-        <v>14.0826686004351</v>
+        <v>14.03179190751445</v>
       </c>
       <c r="FX6" t="n">
-        <v>14.42764578833693</v>
+        <v>14.47976878612717</v>
       </c>
       <c r="FY6" t="n">
-        <v>13.45641769398114</v>
+        <v>13.40780346820809</v>
       </c>
       <c r="FZ6" t="n">
-        <v>13.78287736981041</v>
+        <v>13.83267100192678</v>
       </c>
       <c r="GA6" t="n">
         <v>0.249330835117773</v>
@@ -5093,7 +5093,7 @@
         <v>25.31745835903763</v>
       </c>
       <c r="HV6" t="n">
-        <v>0.2408750302151317</v>
+        <v>0.2428949903660886</v>
       </c>
     </row>
     <row r="7">
@@ -5137,19 +5137,19 @@
         <v>519</v>
       </c>
       <c r="J7" t="n">
-        <v>7951</v>
+        <v>7986</v>
       </c>
       <c r="K7" t="n">
-        <v>8021</v>
+        <v>7986</v>
       </c>
       <c r="L7" t="n">
-        <v>1768</v>
+        <v>1795</v>
       </c>
       <c r="M7" t="n">
-        <v>1978</v>
+        <v>1955</v>
       </c>
       <c r="N7" t="n">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="O7" t="n">
         <v>15972</v>
@@ -5495,7 +5495,7 @@
         <v>2183</v>
       </c>
       <c r="DZ7" t="n">
-        <v>1750</v>
+        <v>1777</v>
       </c>
       <c r="EA7" t="n">
         <v>144</v>
@@ -5642,16 +5642,16 @@
         <v>0.577639751552795</v>
       </c>
       <c r="FW7" t="n">
-        <v>15.25600553389511</v>
+        <v>15.18914350112697</v>
       </c>
       <c r="FX7" t="n">
-        <v>14.43205335993018</v>
+        <v>14.49530428249436</v>
       </c>
       <c r="FY7" t="n">
-        <v>14.58037982643693</v>
+        <v>14.51647883796644</v>
       </c>
       <c r="FZ7" t="n">
-        <v>13.85742426131405</v>
+        <v>13.91815677435512</v>
       </c>
       <c r="GA7" t="n">
         <v>0.2785549368463942</v>
@@ -5795,7 +5795,7 @@
         <v>25.18276412384296</v>
       </c>
       <c r="HV7" t="n">
-        <v>0.22236196704817</v>
+        <v>0.2247683446030553</v>
       </c>
     </row>
     <row r="8">
@@ -5839,16 +5839,16 @@
         <v>-24</v>
       </c>
       <c r="J8" t="n">
-        <v>8283</v>
+        <v>8312</v>
       </c>
       <c r="K8" t="n">
-        <v>8338</v>
+        <v>8309</v>
       </c>
       <c r="L8" t="n">
-        <v>2235</v>
+        <v>2259</v>
       </c>
       <c r="M8" t="n">
-        <v>2163</v>
+        <v>2142</v>
       </c>
       <c r="N8" t="n">
         <v>1229</v>
@@ -6199,7 +6199,7 @@
         <v>2496</v>
       </c>
       <c r="DZ8" t="n">
-        <v>2214</v>
+        <v>2238</v>
       </c>
       <c r="EA8" t="n">
         <v>149</v>
@@ -6346,16 +6346,16 @@
         <v>0.5892857142857143</v>
       </c>
       <c r="FW8" t="n">
-        <v>14.21529639019679</v>
+        <v>14.16570019249278</v>
       </c>
       <c r="FX8" t="n">
-        <v>14.30975053969777</v>
+        <v>14.35969430737754</v>
       </c>
       <c r="FY8" t="n">
-        <v>13.41964264155499</v>
+        <v>13.37282242540905</v>
       </c>
       <c r="FZ8" t="n">
-        <v>13.70564883665148</v>
+        <v>13.75348417378746</v>
       </c>
       <c r="GA8" t="n">
         <v>0.3140584984499259</v>
@@ -6499,7 +6499,7 @@
         <v>25.41776429809359</v>
       </c>
       <c r="HV8" t="n">
-        <v>0.2698297718218037</v>
+        <v>0.2717757459095284</v>
       </c>
     </row>
     <row r="9">
@@ -6543,19 +6543,19 @@
         <v>275</v>
       </c>
       <c r="J9" t="n">
-        <v>8279</v>
+        <v>8315</v>
       </c>
       <c r="K9" t="n">
-        <v>8335</v>
+        <v>8299</v>
       </c>
       <c r="L9" t="n">
-        <v>2131</v>
+        <v>2159</v>
       </c>
       <c r="M9" t="n">
-        <v>2386</v>
+        <v>2355</v>
       </c>
       <c r="N9" t="n">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="O9" t="n">
         <v>16614</v>
@@ -6903,7 +6903,7 @@
         <v>2502</v>
       </c>
       <c r="DZ9" t="n">
-        <v>2111</v>
+        <v>2139</v>
       </c>
       <c r="EA9" t="n">
         <v>185</v>
@@ -7050,16 +7050,16 @@
         <v>0.5777310924369747</v>
       </c>
       <c r="FW9" t="n">
-        <v>14.23987196521319</v>
+        <v>14.17822008418521</v>
       </c>
       <c r="FX9" t="n">
-        <v>14.33330533893221</v>
+        <v>14.39548138329919</v>
       </c>
       <c r="FY9" t="n">
-        <v>13.64666022466481</v>
+        <v>13.58757666867108</v>
       </c>
       <c r="FZ9" t="n">
-        <v>13.70916616676665</v>
+        <v>13.76863477527413</v>
       </c>
       <c r="GA9" t="n">
         <v>0.2914442162902122</v>
@@ -7203,7 +7203,7 @@
         <v>25.32877296587927</v>
       </c>
       <c r="HV9" t="n">
-        <v>0.257398236501993</v>
+        <v>0.2596512327119663</v>
       </c>
     </row>
     <row r="10">
@@ -7247,19 +7247,19 @@
         <v>198</v>
       </c>
       <c r="J10" t="n">
-        <v>8342</v>
+        <v>8383</v>
       </c>
       <c r="K10" t="n">
-        <v>8412</v>
+        <v>8371</v>
       </c>
       <c r="L10" t="n">
-        <v>1830</v>
+        <v>1860</v>
       </c>
       <c r="M10" t="n">
-        <v>2065</v>
+        <v>2032</v>
       </c>
       <c r="N10" t="n">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="O10" t="n">
         <v>16754</v>
@@ -7605,7 +7605,7 @@
         <v>2099</v>
       </c>
       <c r="DZ10" t="n">
-        <v>1816</v>
+        <v>1846</v>
       </c>
       <c r="EA10" t="n">
         <v>131</v>
@@ -7752,16 +7752,16 @@
         <v>0.625974025974026</v>
       </c>
       <c r="FW10" t="n">
-        <v>13.68729321505634</v>
+        <v>13.62035070976977</v>
       </c>
       <c r="FX10" t="n">
-        <v>14.60777460770328</v>
+        <v>14.6793214669693</v>
       </c>
       <c r="FY10" t="n">
-        <v>13.10990170222968</v>
+        <v>13.04578313253012</v>
       </c>
       <c r="FZ10" t="n">
-        <v>14.03563956252972</v>
+        <v>14.10438418349062</v>
       </c>
       <c r="GA10" t="n">
         <v>0.2846021902625676</v>
@@ -7905,7 +7905,7 @@
         <v>25.30586963237566</v>
       </c>
       <c r="HV10" t="n">
-        <v>0.2193718532725965</v>
+        <v>0.2218776094476917</v>
       </c>
     </row>
     <row r="11">
@@ -7949,19 +7949,19 @@
         <v>232</v>
       </c>
       <c r="J11" t="n">
-        <v>8086</v>
+        <v>8117</v>
       </c>
       <c r="K11" t="n">
-        <v>8150</v>
+        <v>8119</v>
       </c>
       <c r="L11" t="n">
-        <v>1997</v>
+        <v>2022</v>
       </c>
       <c r="M11" t="n">
-        <v>2353</v>
+        <v>2328</v>
       </c>
       <c r="N11" t="n">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="O11" t="n">
         <v>16236</v>
@@ -8307,7 +8307,7 @@
         <v>2320</v>
       </c>
       <c r="DZ11" t="n">
-        <v>1992</v>
+        <v>2017</v>
       </c>
       <c r="EA11" t="n">
         <v>168</v>
@@ -8454,16 +8454,16 @@
         <v>0.5822784810126582</v>
       </c>
       <c r="FW11" t="n">
-        <v>14.24105861983676</v>
+        <v>14.18666995195269</v>
       </c>
       <c r="FX11" t="n">
-        <v>14.99469938650307</v>
+        <v>15.05195221086341</v>
       </c>
       <c r="FY11" t="n">
-        <v>13.63905515706159</v>
+        <v>13.58696562769496</v>
       </c>
       <c r="FZ11" t="n">
-        <v>14.40246625766871</v>
+        <v>14.45745781500185</v>
       </c>
       <c r="GA11" t="n">
         <v>0.300123677339563</v>
@@ -8607,7 +8607,7 @@
         <v>25.47044072948328</v>
       </c>
       <c r="HV11" t="n">
-        <v>0.2469700717289142</v>
+        <v>0.2491068128618948</v>
       </c>
     </row>
     <row r="12">
@@ -8651,19 +8651,19 @@
         <v>93</v>
       </c>
       <c r="J12" t="n">
-        <v>7928</v>
+        <v>7954</v>
       </c>
       <c r="K12" t="n">
-        <v>7984</v>
+        <v>7958</v>
       </c>
       <c r="L12" t="n">
-        <v>2126</v>
+        <v>2148</v>
       </c>
       <c r="M12" t="n">
-        <v>1842</v>
+        <v>1820</v>
       </c>
       <c r="N12" t="n">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="O12" t="n">
         <v>15912</v>
@@ -9009,7 +9009,7 @@
         <v>2519</v>
       </c>
       <c r="DZ12" t="n">
-        <v>2111</v>
+        <v>2133</v>
       </c>
       <c r="EA12" t="n">
         <v>113</v>
@@ -9156,16 +9156,16 @@
         <v>0.5725</v>
       </c>
       <c r="FW12" t="n">
-        <v>15.24597628657921</v>
+        <v>15.19614030676389</v>
       </c>
       <c r="FX12" t="n">
-        <v>14.59041833667335</v>
+        <v>14.63808745916059</v>
       </c>
       <c r="FY12" t="n">
-        <v>14.74220484359233</v>
+        <v>14.69401558964043</v>
       </c>
       <c r="FZ12" t="n">
-        <v>13.89728206412826</v>
+        <v>13.94268660467454</v>
       </c>
       <c r="GA12" t="n">
         <v>0.266212099231104</v>
@@ -9309,7 +9309,7 @@
         <v>25.69552669552669</v>
       </c>
       <c r="HV12" t="n">
-        <v>0.2681634712411705</v>
+        <v>0.2700528036208197</v>
       </c>
     </row>
     <row r="13">
@@ -9344,7 +9344,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>237059.7</v>
+        <v>237060</v>
       </c>
       <c r="H13" t="n">
         <v>82</v>
@@ -9353,19 +9353,19 @@
         <v>120</v>
       </c>
       <c r="J13" t="n">
-        <v>8005</v>
+        <v>8043</v>
       </c>
       <c r="K13" t="n">
-        <v>8058</v>
+        <v>8020</v>
       </c>
       <c r="L13" t="n">
-        <v>1758</v>
+        <v>1788</v>
       </c>
       <c r="M13" t="n">
-        <v>2097</v>
+        <v>2069</v>
       </c>
       <c r="N13" t="n">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="O13" t="n">
         <v>16063</v>
@@ -9713,7 +9713,7 @@
         <v>2057</v>
       </c>
       <c r="DZ13" t="n">
-        <v>1748</v>
+        <v>1778</v>
       </c>
       <c r="EA13" t="n">
         <v>170</v>
@@ -9854,22 +9854,22 @@
         <v>0.03850415512465374</v>
       </c>
       <c r="FU13" t="n">
-        <v>97.57339606858524</v>
+        <v>97.57327258921792</v>
       </c>
       <c r="FV13" t="n">
         <v>0.6080691642651297</v>
       </c>
       <c r="FW13" t="n">
-        <v>14.74437226733292</v>
+        <v>14.67474822827303</v>
       </c>
       <c r="FX13" t="n">
-        <v>14.77177959791512</v>
+        <v>14.84177057356609</v>
       </c>
       <c r="FY13" t="n">
-        <v>14.01971267957527</v>
+        <v>13.95351237100584</v>
       </c>
       <c r="FZ13" t="n">
-        <v>14.14470091834202</v>
+        <v>14.21172069825436</v>
       </c>
       <c r="GA13" t="n">
         <v>0.2311733800350263</v>
@@ -10013,7 +10013,7 @@
         <v>26.07930107526882</v>
       </c>
       <c r="HV13" t="n">
-        <v>0.2196127420362274</v>
+        <v>0.2223051100335696</v>
       </c>
     </row>
     <row r="14">
@@ -10057,19 +10057,19 @@
         <v>-820</v>
       </c>
       <c r="J14" t="n">
-        <v>8148</v>
+        <v>8171</v>
       </c>
       <c r="K14" t="n">
-        <v>8219</v>
+        <v>8196</v>
       </c>
       <c r="L14" t="n">
-        <v>1801</v>
+        <v>1821</v>
       </c>
       <c r="M14" t="n">
-        <v>2075</v>
+        <v>2058</v>
       </c>
       <c r="N14" t="n">
-        <v>996</v>
+        <v>999</v>
       </c>
       <c r="O14" t="n">
         <v>16367</v>
@@ -10417,7 +10417,7 @@
         <v>2014</v>
       </c>
       <c r="DZ14" t="n">
-        <v>1786</v>
+        <v>1806</v>
       </c>
       <c r="EA14" t="n">
         <v>119</v>
@@ -10564,16 +10564,16 @@
         <v>0.5376344086021505</v>
       </c>
       <c r="FW14" t="n">
-        <v>14.69350760922926</v>
+        <v>14.65214783992167</v>
       </c>
       <c r="FX14" t="n">
-        <v>14.2763474875289</v>
+        <v>14.31641044411908</v>
       </c>
       <c r="FY14" t="n">
-        <v>14.05506872852234</v>
+        <v>14.01550605801003</v>
       </c>
       <c r="FZ14" t="n">
-        <v>13.66283002798394</v>
+        <v>13.70117130307467</v>
       </c>
       <c r="GA14" t="n">
         <v>0.2224041479055806</v>
@@ -10717,7 +10717,7 @@
         <v>25.80618181818182</v>
       </c>
       <c r="HV14" t="n">
-        <v>0.2210358370152185</v>
+        <v>0.2228613388814099</v>
       </c>
     </row>
     <row r="15">
@@ -10761,19 +10761,19 @@
         <v>914</v>
       </c>
       <c r="J15" t="n">
-        <v>8211</v>
+        <v>8242</v>
       </c>
       <c r="K15" t="n">
-        <v>8269</v>
+        <v>8238</v>
       </c>
       <c r="L15" t="n">
-        <v>1931</v>
+        <v>1955</v>
       </c>
       <c r="M15" t="n">
-        <v>1975</v>
+        <v>1954</v>
       </c>
       <c r="N15" t="n">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="O15" t="n">
         <v>16480</v>
@@ -11119,7 +11119,7 @@
         <v>2264</v>
       </c>
       <c r="DZ15" t="n">
-        <v>1922</v>
+        <v>1946</v>
       </c>
       <c r="EA15" t="n">
         <v>132</v>
@@ -11266,16 +11266,16 @@
         <v>0.5924276169265034</v>
       </c>
       <c r="FW15" t="n">
-        <v>14.07318231640482</v>
+        <v>14.02024993933511</v>
       </c>
       <c r="FX15" t="n">
-        <v>14.8391703954529</v>
+        <v>14.89501092498179</v>
       </c>
       <c r="FY15" t="n">
-        <v>13.5377907684813</v>
+        <v>13.48687211841786</v>
       </c>
       <c r="FZ15" t="n">
-        <v>14.17380578062644</v>
+        <v>14.22714251031804</v>
       </c>
       <c r="GA15" t="n">
         <v>0.2773006134969325</v>
@@ -11419,7 +11419,7 @@
         <v>25.41835422693667</v>
       </c>
       <c r="HV15" t="n">
-        <v>0.2351723298014858</v>
+        <v>0.2371997088085416</v>
       </c>
     </row>
     <row r="16">
@@ -11463,19 +11463,19 @@
         <v>-691</v>
       </c>
       <c r="J16" t="n">
-        <v>8463</v>
+        <v>8494</v>
       </c>
       <c r="K16" t="n">
-        <v>8517</v>
+        <v>8486</v>
       </c>
       <c r="L16" t="n">
-        <v>2217</v>
+        <v>2243</v>
       </c>
       <c r="M16" t="n">
-        <v>2470</v>
+        <v>2441</v>
       </c>
       <c r="N16" t="n">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="O16" t="n">
         <v>16980</v>
@@ -11819,7 +11819,7 @@
         <v>2617</v>
       </c>
       <c r="DZ16" t="n">
-        <v>2207</v>
+        <v>2233</v>
       </c>
       <c r="EA16" t="n">
         <v>158</v>
@@ -11966,16 +11966,16 @@
         <v>0.6116504854368932</v>
       </c>
       <c r="FW16" t="n">
-        <v>14.159080704242</v>
+        <v>14.10740522721921</v>
       </c>
       <c r="FX16" t="n">
-        <v>13.87010684513326</v>
+        <v>13.92077539476785</v>
       </c>
       <c r="FY16" t="n">
-        <v>13.59450549450549</v>
+        <v>13.54489051094891</v>
       </c>
       <c r="FZ16" t="n">
-        <v>13.30314664788071</v>
+        <v>13.35174404902192</v>
       </c>
       <c r="GA16" t="n">
         <v>0.2547948854555141</v>
@@ -12119,7 +12119,7 @@
         <v>25.22757817697938</v>
       </c>
       <c r="HV16" t="n">
-        <v>0.2619638426090039</v>
+        <v>0.2640687544148811</v>
       </c>
     </row>
     <row r="17">
@@ -12163,16 +12163,16 @@
         <v>-983</v>
       </c>
       <c r="J17" t="n">
-        <v>8360</v>
+        <v>8389</v>
       </c>
       <c r="K17" t="n">
-        <v>8419</v>
+        <v>8390</v>
       </c>
       <c r="L17" t="n">
-        <v>1841</v>
+        <v>1863</v>
       </c>
       <c r="M17" t="n">
-        <v>2591</v>
+        <v>2571</v>
       </c>
       <c r="N17" t="n">
         <v>979</v>
@@ -12521,7 +12521,7 @@
         <v>1995</v>
       </c>
       <c r="DZ17" t="n">
-        <v>1838</v>
+        <v>1860</v>
       </c>
       <c r="EA17" t="n">
         <v>168</v>
@@ -12668,16 +12668,16 @@
         <v>0.5663716814159292</v>
       </c>
       <c r="FW17" t="n">
-        <v>14.18200956937799</v>
+        <v>14.13298366909048</v>
       </c>
       <c r="FX17" t="n">
-        <v>14.07511580947856</v>
+        <v>14.12376638855781</v>
       </c>
       <c r="FY17" t="n">
-        <v>13.65911483253589</v>
+        <v>13.61189653117177</v>
       </c>
       <c r="FZ17" t="n">
-        <v>13.43710654472028</v>
+        <v>13.48355184743743</v>
       </c>
       <c r="GA17" t="n">
         <v>0.2698859825620389</v>
@@ -12821,7 +12821,7 @@
         <v>25.99993295340262</v>
       </c>
       <c r="HV17" t="n">
-        <v>0.2202153110047847</v>
+        <v>0.2220765287876982</v>
       </c>
     </row>
     <row r="18">
@@ -12865,19 +12865,19 @@
         <v>631</v>
       </c>
       <c r="J18" t="n">
-        <v>7782</v>
+        <v>7811</v>
       </c>
       <c r="K18" t="n">
-        <v>7828</v>
+        <v>7799</v>
       </c>
       <c r="L18" t="n">
-        <v>1739</v>
+        <v>1761</v>
       </c>
       <c r="M18" t="n">
-        <v>1752</v>
+        <v>1726</v>
       </c>
       <c r="N18" t="n">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="O18" t="n">
         <v>15610</v>
@@ -13223,7 +13223,7 @@
         <v>2035</v>
       </c>
       <c r="DZ18" t="n">
-        <v>1722</v>
+        <v>1744</v>
       </c>
       <c r="EA18" t="n">
         <v>113</v>
@@ -13370,16 +13370,16 @@
         <v>0.5853658536585366</v>
       </c>
       <c r="FW18" t="n">
-        <v>15.82000771010023</v>
+        <v>15.76127256433235</v>
       </c>
       <c r="FX18" t="n">
-        <v>14.51822943280531</v>
+        <v>14.5722143864598</v>
       </c>
       <c r="FY18" t="n">
-        <v>15.00655358519661</v>
+        <v>14.95083856100371</v>
       </c>
       <c r="FZ18" t="n">
-        <v>13.86234031681145</v>
+        <v>13.91388639569175</v>
       </c>
       <c r="GA18" t="n">
         <v>0.2073236402800215</v>
@@ -13523,7 +13523,7 @@
         <v>26.16539351851852</v>
       </c>
       <c r="HV18" t="n">
-        <v>0.2234644050372655</v>
+        <v>0.2254512866470362</v>
       </c>
     </row>
     <row r="19">
@@ -13567,19 +13567,19 @@
         <v>338</v>
       </c>
       <c r="J19" t="n">
-        <v>8206</v>
+        <v>8244</v>
       </c>
       <c r="K19" t="n">
-        <v>8268</v>
+        <v>8230</v>
       </c>
       <c r="L19" t="n">
-        <v>2246</v>
+        <v>2278</v>
       </c>
       <c r="M19" t="n">
-        <v>2189</v>
+        <v>2161</v>
       </c>
       <c r="N19" t="n">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="O19" t="n">
         <v>16474</v>
@@ -13927,7 +13927,7 @@
         <v>2656</v>
       </c>
       <c r="DZ19" t="n">
-        <v>2227</v>
+        <v>2259</v>
       </c>
       <c r="EA19" t="n">
         <v>181</v>
@@ -14074,16 +14074,16 @@
         <v>0.5378973105134475</v>
       </c>
       <c r="FW19" t="n">
-        <v>14.02810138922739</v>
+        <v>13.96344007763222</v>
       </c>
       <c r="FX19" t="n">
-        <v>14.74908079342041</v>
+        <v>14.81718104495747</v>
       </c>
       <c r="FY19" t="n">
-        <v>13.34261515963929</v>
+        <v>13.2811135371179</v>
       </c>
       <c r="FZ19" t="n">
-        <v>14.09438800193517</v>
+        <v>14.15946537059538</v>
       </c>
       <c r="GA19" t="n">
         <v>0.2852901484480432</v>
@@ -14227,7 +14227,7 @@
         <v>25.46004293161607</v>
       </c>
       <c r="HV19" t="n">
-        <v>0.2737021691445284</v>
+        <v>0.2763221737020864</v>
       </c>
     </row>
     <row r="20">
@@ -14271,19 +14271,19 @@
         <v>-369</v>
       </c>
       <c r="J20" t="n">
-        <v>8281</v>
+        <v>8310</v>
       </c>
       <c r="K20" t="n">
-        <v>8344</v>
+        <v>8315</v>
       </c>
       <c r="L20" t="n">
-        <v>2240</v>
+        <v>2263</v>
       </c>
       <c r="M20" t="n">
-        <v>2092</v>
+        <v>2065</v>
       </c>
       <c r="N20" t="n">
-        <v>1038</v>
+        <v>1045</v>
       </c>
       <c r="O20" t="n">
         <v>16625</v>
@@ -14631,7 +14631,7 @@
         <v>2610</v>
       </c>
       <c r="DZ20" t="n">
-        <v>2236</v>
+        <v>2259</v>
       </c>
       <c r="EA20" t="n">
         <v>134</v>
@@ -14778,16 +14778,16 @@
         <v>0.5620608899297423</v>
       </c>
       <c r="FW20" t="n">
-        <v>14.3039971017993</v>
+        <v>14.25407942238267</v>
       </c>
       <c r="FX20" t="n">
-        <v>14.28674496644295</v>
+        <v>14.3365724594107</v>
       </c>
       <c r="FY20" t="n">
-        <v>13.74327979712595</v>
+        <v>13.69531889290012</v>
       </c>
       <c r="FZ20" t="n">
-        <v>13.6722794822627</v>
+        <v>13.71996392062537</v>
       </c>
       <c r="GA20" t="n">
         <v>0.3802873640392104</v>
@@ -14931,7 +14931,7 @@
         <v>25.69795066413662</v>
       </c>
       <c r="HV20" t="n">
-        <v>0.2704987320371936</v>
+        <v>0.2723225030084236</v>
       </c>
     </row>
     <row r="21">
@@ -14975,19 +14975,19 @@
         <v>-427</v>
       </c>
       <c r="J21" t="n">
-        <v>8410</v>
+        <v>8439</v>
       </c>
       <c r="K21" t="n">
-        <v>8465</v>
+        <v>8436</v>
       </c>
       <c r="L21" t="n">
-        <v>2069</v>
+        <v>2091</v>
       </c>
       <c r="M21" t="n">
-        <v>2088</v>
+        <v>2064</v>
       </c>
       <c r="N21" t="n">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="O21" t="n">
         <v>16875</v>
@@ -15335,7 +15335,7 @@
         <v>2401</v>
       </c>
       <c r="DZ21" t="n">
-        <v>2053</v>
+        <v>2075</v>
       </c>
       <c r="EA21" t="n">
         <v>126</v>
@@ -15482,16 +15482,16 @@
         <v>0.624390243902439</v>
       </c>
       <c r="FW21" t="n">
-        <v>13.75372175980975</v>
+        <v>13.70645811115061</v>
       </c>
       <c r="FX21" t="n">
-        <v>14.34036621382162</v>
+        <v>14.38966334755808</v>
       </c>
       <c r="FY21" t="n">
-        <v>13.16567181926278</v>
+        <v>13.12042896077734</v>
       </c>
       <c r="FZ21" t="n">
-        <v>13.75782634376846</v>
+        <v>13.80512091038407</v>
       </c>
       <c r="GA21" t="n">
         <v>0.3492893537141325</v>
@@ -15635,7 +15635,7 @@
         <v>25.38478393183201</v>
       </c>
       <c r="HV21" t="n">
-        <v>0.2460166468489893</v>
+        <v>0.2477781727692855</v>
       </c>
     </row>
     <row r="22">
@@ -15679,19 +15679,19 @@
         <v>-452</v>
       </c>
       <c r="J22" t="n">
-        <v>8389</v>
+        <v>8424</v>
       </c>
       <c r="K22" t="n">
-        <v>8467</v>
+        <v>8432</v>
       </c>
       <c r="L22" t="n">
-        <v>2405</v>
+        <v>2434</v>
       </c>
       <c r="M22" t="n">
-        <v>1726</v>
+        <v>1698</v>
       </c>
       <c r="N22" t="n">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="O22" t="n">
         <v>16856</v>
@@ -16039,7 +16039,7 @@
         <v>2695</v>
       </c>
       <c r="DZ22" t="n">
-        <v>2392</v>
+        <v>2421</v>
       </c>
       <c r="EA22" t="n">
         <v>78</v>
@@ -16186,16 +16186,16 @@
         <v>0.5933806146572104</v>
       </c>
       <c r="FW22" t="n">
-        <v>14.17652878769818</v>
+        <v>14.1176282051282</v>
       </c>
       <c r="FX22" t="n">
-        <v>14.09390575174206</v>
+        <v>14.15240749525617</v>
       </c>
       <c r="FY22" t="n">
-        <v>13.64294910001192</v>
+        <v>13.58626543209876</v>
       </c>
       <c r="FZ22" t="n">
-        <v>13.50205503720326</v>
+        <v>13.55810009487666</v>
       </c>
       <c r="GA22" t="n">
         <v>0.2833783783783784</v>
@@ -16339,7 +16339,7 @@
         <v>25.14818355640535</v>
       </c>
       <c r="HV22" t="n">
-        <v>0.2866849445702706</v>
+        <v>0.2889363722697056</v>
       </c>
     </row>
     <row r="23">
@@ -16383,19 +16383,19 @@
         <v>422</v>
       </c>
       <c r="J23" t="n">
-        <v>8171</v>
+        <v>8201</v>
       </c>
       <c r="K23" t="n">
-        <v>8232</v>
+        <v>8202</v>
       </c>
       <c r="L23" t="n">
-        <v>2325</v>
+        <v>2351</v>
       </c>
       <c r="M23" t="n">
-        <v>1935</v>
+        <v>1912</v>
       </c>
       <c r="N23" t="n">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="O23" t="n">
         <v>16403</v>
@@ -16741,7 +16741,7 @@
         <v>2869</v>
       </c>
       <c r="DZ23" t="n">
-        <v>2295</v>
+        <v>2321</v>
       </c>
       <c r="EA23" t="n">
         <v>133</v>
@@ -16888,16 +16888,16 @@
         <v>0.5876923076923077</v>
       </c>
       <c r="FW23" t="n">
-        <v>14.89495777750581</v>
+        <v>14.84047067430801</v>
       </c>
       <c r="FX23" t="n">
-        <v>14.26789358600583</v>
+        <v>14.32008046817849</v>
       </c>
       <c r="FY23" t="n">
-        <v>14.40167666136336</v>
+        <v>14.34899402511889</v>
       </c>
       <c r="FZ23" t="n">
-        <v>13.72745383867833</v>
+        <v>13.77766398439405</v>
       </c>
       <c r="GA23" t="n">
         <v>0.2637833356363134</v>
@@ -17041,7 +17041,7 @@
         <v>25.4855438117968</v>
       </c>
       <c r="HV23" t="n">
-        <v>0.2845428956064129</v>
+        <v>0.2866723570296305</v>
       </c>
     </row>
     <row r="24">
@@ -17085,19 +17085,19 @@
         <v>428</v>
       </c>
       <c r="J24" t="n">
-        <v>7945</v>
+        <v>7980</v>
       </c>
       <c r="K24" t="n">
-        <v>8017</v>
+        <v>7982</v>
       </c>
       <c r="L24" t="n">
-        <v>2028</v>
+        <v>2056</v>
       </c>
       <c r="M24" t="n">
-        <v>1765</v>
+        <v>1735</v>
       </c>
       <c r="N24" t="n">
-        <v>1197</v>
+        <v>1201</v>
       </c>
       <c r="O24" t="n">
         <v>15962</v>
@@ -17445,7 +17445,7 @@
         <v>2374</v>
       </c>
       <c r="DZ24" t="n">
-        <v>2007</v>
+        <v>2035</v>
       </c>
       <c r="EA24" t="n">
         <v>121</v>
@@ -17592,16 +17592,16 @@
         <v>0.6152219873150105</v>
       </c>
       <c r="FW24" t="n">
-        <v>15.7931655129012</v>
+        <v>15.72389724310777</v>
       </c>
       <c r="FX24" t="n">
-        <v>14.14285892478483</v>
+        <v>14.20487346529692</v>
       </c>
       <c r="FY24" t="n">
-        <v>14.96021397105097</v>
+        <v>14.89459899749373</v>
       </c>
       <c r="FZ24" t="n">
-        <v>13.50817013845578</v>
+        <v>13.56740165372087</v>
       </c>
       <c r="GA24" t="n">
         <v>0.2688564476885645</v>
@@ -17745,7 +17745,7 @@
         <v>25.57003875968992</v>
       </c>
       <c r="HV24" t="n">
-        <v>0.255254877281309</v>
+        <v>0.2576441102756892</v>
       </c>
     </row>
     <row r="25">
@@ -17780,7 +17780,7 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>237059.7</v>
+        <v>237060</v>
       </c>
       <c r="H25" t="n">
         <v>82</v>
@@ -17789,19 +17789,19 @@
         <v>-509</v>
       </c>
       <c r="J25" t="n">
-        <v>7999</v>
+        <v>8019</v>
       </c>
       <c r="K25" t="n">
-        <v>8071</v>
+        <v>8051</v>
       </c>
       <c r="L25" t="n">
-        <v>1782</v>
+        <v>1800</v>
       </c>
       <c r="M25" t="n">
-        <v>1923</v>
+        <v>1905</v>
       </c>
       <c r="N25" t="n">
-        <v>836</v>
+        <v>841</v>
       </c>
       <c r="O25" t="n">
         <v>16070</v>
@@ -18147,7 +18147,7 @@
         <v>2039</v>
       </c>
       <c r="DZ25" t="n">
-        <v>1773</v>
+        <v>1791</v>
       </c>
       <c r="EA25" t="n">
         <v>119</v>
@@ -18288,22 +18288,22 @@
         <v>0.03722760290556901</v>
       </c>
       <c r="FU25" t="n">
-        <v>97.61591700318526</v>
+        <v>97.61579347000759</v>
       </c>
       <c r="FV25" t="n">
         <v>0.5552147239263804</v>
       </c>
       <c r="FW25" t="n">
-        <v>15.01375171896487</v>
+        <v>14.97630627260257</v>
       </c>
       <c r="FX25" t="n">
-        <v>14.49197125511089</v>
+        <v>14.52800894298845</v>
       </c>
       <c r="FY25" t="n">
-        <v>14.44935616952119</v>
+        <v>14.41331836887392</v>
       </c>
       <c r="FZ25" t="n">
-        <v>13.84423243712055</v>
+        <v>13.87866103589616</v>
       </c>
       <c r="GA25" t="n">
         <v>0.2520913086629803</v>
@@ -18447,7 +18447,7 @@
         <v>25.52886115444618</v>
       </c>
       <c r="HV25" t="n">
-        <v>0.2227778472309039</v>
+        <v>0.2244668911335578</v>
       </c>
     </row>
     <row r="26">
@@ -18482,7 +18482,7 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>237060</v>
+        <v>237063</v>
       </c>
       <c r="H26" t="n">
         <v>82</v>
@@ -18491,19 +18491,19 @@
         <v>-819</v>
       </c>
       <c r="J26" t="n">
-        <v>7950</v>
+        <v>7979</v>
       </c>
       <c r="K26" t="n">
-        <v>8007</v>
+        <v>7978</v>
       </c>
       <c r="L26" t="n">
-        <v>1987</v>
+        <v>2010</v>
       </c>
       <c r="M26" t="n">
-        <v>2237</v>
+        <v>2215</v>
       </c>
       <c r="N26" t="n">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="O26" t="n">
         <v>15957</v>
@@ -18849,7 +18849,7 @@
         <v>2098</v>
       </c>
       <c r="DZ26" t="n">
-        <v>1980</v>
+        <v>2003</v>
       </c>
       <c r="EA26" t="n">
         <v>176</v>
@@ -18990,22 +18990,22 @@
         <v>0.04215801886792453</v>
       </c>
       <c r="FU26" t="n">
-        <v>96.92938496583143</v>
+        <v>96.92815833765708</v>
       </c>
       <c r="FV26" t="n">
         <v>0.5371428571428571</v>
       </c>
       <c r="FW26" t="n">
-        <v>15.14786163522013</v>
+        <v>15.09280611605464</v>
       </c>
       <c r="FX26" t="n">
-        <v>14.56656675409017</v>
+        <v>14.61989220355979</v>
       </c>
       <c r="FY26" t="n">
-        <v>14.58607547169811</v>
+        <v>14.53306178719138</v>
       </c>
       <c r="FZ26" t="n">
-        <v>13.9582864993131</v>
+        <v>14.00940085234395</v>
       </c>
       <c r="GA26" t="n">
         <v>0.2896927935687625</v>
@@ -19149,7 +19149,7 @@
         <v>25.36236900603366</v>
       </c>
       <c r="HV26" t="n">
-        <v>0.249937106918239</v>
+        <v>0.2519112670760747</v>
       </c>
     </row>
     <row r="27">
@@ -19193,19 +19193,19 @@
         <v>52</v>
       </c>
       <c r="J27" t="n">
-        <v>8217</v>
+        <v>8250</v>
       </c>
       <c r="K27" t="n">
-        <v>8290</v>
+        <v>8257</v>
       </c>
       <c r="L27" t="n">
-        <v>2382</v>
+        <v>2411</v>
       </c>
       <c r="M27" t="n">
-        <v>2329</v>
+        <v>2301</v>
       </c>
       <c r="N27" t="n">
-        <v>1011</v>
+        <v>1014</v>
       </c>
       <c r="O27" t="n">
         <v>16507</v>
@@ -19551,7 +19551,7 @@
         <v>2775</v>
       </c>
       <c r="DZ27" t="n">
-        <v>2365</v>
+        <v>2394</v>
       </c>
       <c r="EA27" t="n">
         <v>159</v>
@@ -19698,16 +19698,16 @@
         <v>0.6537467700258398</v>
       </c>
       <c r="FW27" t="n">
-        <v>14.50126566873555</v>
+        <v>14.4432606060606</v>
       </c>
       <c r="FX27" t="n">
-        <v>14.33089264173703</v>
+        <v>14.38816761535667</v>
       </c>
       <c r="FY27" t="n">
-        <v>13.88180601192649</v>
+        <v>13.82627878787879</v>
       </c>
       <c r="FZ27" t="n">
-        <v>13.7643425814234</v>
+        <v>13.81935327600824</v>
       </c>
       <c r="GA27" t="n">
         <v>0.3086640120829329</v>
@@ -19851,7 +19851,7 @@
         <v>25.3743397573162</v>
       </c>
       <c r="HV27" t="n">
-        <v>0.2898868200073019</v>
+        <v>0.2922424242424242</v>
       </c>
     </row>
     <row r="28">
@@ -19895,19 +19895,19 @@
         <v>-655</v>
       </c>
       <c r="J28" t="n">
-        <v>8291</v>
+        <v>8320</v>
       </c>
       <c r="K28" t="n">
-        <v>8352</v>
+        <v>8323</v>
       </c>
       <c r="L28" t="n">
-        <v>2121</v>
+        <v>2149</v>
       </c>
       <c r="M28" t="n">
-        <v>2387</v>
+        <v>2364</v>
       </c>
       <c r="N28" t="n">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="O28" t="n">
         <v>16643</v>
@@ -20253,7 +20253,7 @@
         <v>2325</v>
       </c>
       <c r="DZ28" t="n">
-        <v>2110</v>
+        <v>2138</v>
       </c>
       <c r="EA28" t="n">
         <v>142</v>
@@ -20400,16 +20400,16 @@
         <v>0.5573333333333333</v>
       </c>
       <c r="FW28" t="n">
-        <v>14.07640815341937</v>
+        <v>14.02734375</v>
       </c>
       <c r="FX28" t="n">
-        <v>14.41002155172414</v>
+        <v>14.4602306860507</v>
       </c>
       <c r="FY28" t="n">
-        <v>13.56999155711012</v>
+        <v>13.52269230769231</v>
       </c>
       <c r="FZ28" t="n">
-        <v>13.84765325670498</v>
+        <v>13.89590291962033</v>
       </c>
       <c r="GA28" t="n">
         <v>0.2657228423631908</v>
@@ -20553,7 +20553,7 @@
         <v>25.82931258106355</v>
       </c>
       <c r="HV28" t="n">
-        <v>0.2558195633819805</v>
+        <v>0.2582932692307692</v>
       </c>
     </row>
     <row r="29">
@@ -20597,19 +20597,19 @@
         <v>-15</v>
       </c>
       <c r="J29" t="n">
-        <v>8227</v>
+        <v>8257</v>
       </c>
       <c r="K29" t="n">
-        <v>8295</v>
+        <v>8265</v>
       </c>
       <c r="L29" t="n">
-        <v>2102</v>
+        <v>2129</v>
       </c>
       <c r="M29" t="n">
-        <v>2233</v>
+        <v>2211</v>
       </c>
       <c r="N29" t="n">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="O29" t="n">
         <v>16522</v>
@@ -20955,7 +20955,7 @@
         <v>2472</v>
       </c>
       <c r="DZ29" t="n">
-        <v>2082</v>
+        <v>2109</v>
       </c>
       <c r="EA29" t="n">
         <v>159</v>
@@ -21102,16 +21102,16 @@
         <v>0.5323275862068966</v>
       </c>
       <c r="FW29" t="n">
-        <v>14.77124103561444</v>
+        <v>14.71757296839046</v>
       </c>
       <c r="FX29" t="n">
-        <v>14.10934297769741</v>
+        <v>14.16055656382335</v>
       </c>
       <c r="FY29" t="n">
-        <v>14.20354928892671</v>
+        <v>14.15194380525615</v>
       </c>
       <c r="FZ29" t="n">
-        <v>13.43159734779988</v>
+        <v>13.48035087719298</v>
       </c>
       <c r="GA29" t="n">
         <v>0.3145237135563617</v>
@@ -21255,7 +21255,7 @@
         <v>25.90141574585635</v>
       </c>
       <c r="HV29" t="n">
-        <v>0.255500182326486</v>
+        <v>0.2578418311735497</v>
       </c>
     </row>
     <row r="30">
@@ -21299,19 +21299,19 @@
         <v>669</v>
       </c>
       <c r="J30" t="n">
-        <v>8157</v>
+        <v>8187</v>
       </c>
       <c r="K30" t="n">
-        <v>8216</v>
+        <v>8186</v>
       </c>
       <c r="L30" t="n">
-        <v>2373</v>
+        <v>2402</v>
       </c>
       <c r="M30" t="n">
-        <v>2569</v>
+        <v>2542</v>
       </c>
       <c r="N30" t="n">
-        <v>1112</v>
+        <v>1115</v>
       </c>
       <c r="O30" t="n">
         <v>16373</v>
@@ -21659,7 +21659,7 @@
         <v>2768</v>
       </c>
       <c r="DZ30" t="n">
-        <v>2343</v>
+        <v>2372</v>
       </c>
       <c r="EA30" t="n">
         <v>203</v>
@@ -21806,16 +21806,16 @@
         <v>0.5889101338432122</v>
       </c>
       <c r="FW30" t="n">
-        <v>14.40468309427486</v>
+        <v>14.35189935263222</v>
       </c>
       <c r="FX30" t="n">
-        <v>14.62524342745862</v>
+        <v>14.67884192523821</v>
       </c>
       <c r="FY30" t="n">
-        <v>13.72400392301091</v>
+        <v>13.67371442530841</v>
       </c>
       <c r="FZ30" t="n">
-        <v>14.00071811100292</v>
+        <v>14.05202785243098</v>
       </c>
       <c r="GA30" t="n">
         <v>0.3350074657255328</v>
@@ -21959,7 +21959,7 @@
         <v>25.46126232741618</v>
       </c>
       <c r="HV30" t="n">
-        <v>0.2909157778595072</v>
+        <v>0.2933919628679614</v>
       </c>
     </row>
     <row r="31">
@@ -22003,19 +22003,19 @@
         <v>396</v>
       </c>
       <c r="J31" t="n">
-        <v>7962</v>
+        <v>7994</v>
       </c>
       <c r="K31" t="n">
-        <v>8015</v>
+        <v>7983</v>
       </c>
       <c r="L31" t="n">
-        <v>2000</v>
+        <v>2030</v>
       </c>
       <c r="M31" t="n">
-        <v>1842</v>
+        <v>1810</v>
       </c>
       <c r="N31" t="n">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="O31" t="n">
         <v>15977</v>
@@ -22363,7 +22363,7 @@
         <v>2284</v>
       </c>
       <c r="DZ31" t="n">
-        <v>1988</v>
+        <v>2018</v>
       </c>
       <c r="EA31" t="n">
         <v>131</v>
@@ -22510,16 +22510,16 @@
         <v>0.5718157181571816</v>
       </c>
       <c r="FW31" t="n">
-        <v>15.37230595327807</v>
+        <v>15.31077057793345</v>
       </c>
       <c r="FX31" t="n">
-        <v>14.30638802245789</v>
+        <v>14.36373543780534</v>
       </c>
       <c r="FY31" t="n">
-        <v>14.51190655614167</v>
+        <v>14.45381536152114</v>
       </c>
       <c r="FZ31" t="n">
-        <v>13.72284466625078</v>
+        <v>13.77785293749217</v>
       </c>
       <c r="GA31" t="n">
         <v>0.2570960698689956</v>
@@ -22663,7 +22663,7 @@
         <v>25.94181459566075</v>
       </c>
       <c r="HV31" t="n">
-        <v>0.2511931675458428</v>
+        <v>0.2539404553415061</v>
       </c>
     </row>
   </sheetData>
